--- a/Assets/Resources/Story/1.xlsx
+++ b/Assets/Resources/Story/1.xlsx
@@ -1,182 +1,720 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="93">
+  <si>
+    <t>医生</t>
+  </si>
+  <si>
+    <t>身体状况怎么样</t>
+  </si>
+  <si>
+    <t>真</t>
+  </si>
+  <si>
+    <t>你是谁（因为手脚被绑而挣扎）</t>
+  </si>
+  <si>
+    <t>精神非常不错呢，我是你的主治医生</t>
+  </si>
+  <si>
+    <t>真的吗</t>
+  </si>
+  <si>
+    <t>真的</t>
+  </si>
+  <si>
+    <t>看起来不像</t>
+  </si>
+  <si>
+    <t>为什么</t>
+  </si>
+  <si>
+    <t>很可疑，而且为什么要绑着我</t>
+  </si>
+  <si>
+    <t>这是必要的处理，你还记得自己是遭了雷击而被人送到这里的吗</t>
+  </si>
+  <si>
+    <t>不记得了</t>
+  </si>
+  <si>
+    <t>名字呢</t>
+  </si>
+  <si>
+    <t>嗯。。。要做些检查，可能要住院</t>
+  </si>
+  <si>
+    <t>信不过你啊，，有没有什么能让我相信你的东西</t>
+  </si>
+  <si>
+    <t>值得被你相信的证据吗，，刚刚，我说过你是被雷击中了才来到这里的</t>
+  </si>
+  <si>
+    <t>而把你从昏迷当中治好的，就是我</t>
+  </si>
+  <si>
+    <t>治好了？</t>
+  </si>
+  <si>
+    <t>现在你能这么生龙活虎，都是我的功劳</t>
+  </si>
+  <si>
+    <t>是说我以前不能动了吗</t>
+  </si>
+  <si>
+    <t>就在那躺着，没准一会就咽气的了</t>
+  </si>
+  <si>
+    <t>多亏了我的治疗，你才能这么精神的活动</t>
+  </si>
+  <si>
+    <t>雷击可是很难治的，会突然造成身体机能紊乱而痉挛</t>
+  </si>
+  <si>
+    <t>所以才说这是必要的处理</t>
+  </si>
+  <si>
+    <t>所以你是我的救命恩人了</t>
+  </si>
+  <si>
+    <t>希望你能这么觉得，但可惜你什么都记不得了</t>
+  </si>
+  <si>
+    <t>算了，之后再来决定要不要信任你</t>
+  </si>
+  <si>
+    <t>那么，可以继续之前的话题了吗</t>
+  </si>
+  <si>
+    <t>我现在什么都不知道，，</t>
+  </si>
+  <si>
+    <t>反正现在有必要先做一下检查</t>
+  </si>
+  <si>
+    <t>你需要在这里住院三天，望你理解</t>
+  </si>
+  <si>
+    <t>那我手上的绑带</t>
+  </si>
+  <si>
+    <t>明天会解开的，今天先观察一下情况</t>
+  </si>
+  <si>
+    <t>现在也只能相信医生了吧，，</t>
+  </si>
+  <si>
+    <t>感谢，这三天将会对你进行检查，你还记得多少东西</t>
+  </si>
+  <si>
+    <t>没准有点什么就想起来了</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接下来就是</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有点什么</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，你对</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>囚徒困境</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的博弈理论还记得吗</t>
+    </r>
+  </si>
+  <si>
+    <t>系统</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（放</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>cg</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>这是为了让你记忆恢复的谈话，我跟你是一起犯罪的同伴</t>
+  </si>
+  <si>
+    <t>欸</t>
+  </si>
+  <si>
+    <t>假设的</t>
+  </si>
+  <si>
+    <t>哦</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>所以现在被抓获，带到了不同的审讯室，被强制要求</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>缄默</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>""</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>坦白</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二选一</t>
+    </r>
+  </si>
+  <si>
+    <t>互相都缄默时证据不足，两人都是刑期两年</t>
+  </si>
+  <si>
+    <t>互相都坦白是，按正常判罚，刑期都是五年</t>
+  </si>
+  <si>
+    <t>一方缄默一方坦白时，缄默的刑期十年，而坦白的将会被释放</t>
+  </si>
+  <si>
+    <t>在这样的情况下，你会选择缄默还是坦白，来跟我回答一下吧</t>
+  </si>
+  <si>
+    <t>坦白</t>
+  </si>
+  <si>
+    <t>那就是正常情况下的五年刑期</t>
+  </si>
+  <si>
+    <t>为什么会选择坦白呢</t>
+  </si>
+  <si>
+    <t>秘密一直藏在心底里会很难受吧，所以只能坦白了</t>
+  </si>
+  <si>
+    <t>所以对自己的罪一开始就决定要坦白</t>
+  </si>
+  <si>
+    <t>可能你会否认，但我没准跟你很相像呢</t>
+  </si>
+  <si>
+    <t>一样的？</t>
+  </si>
+  <si>
+    <t>是，一样的理由，意外吗</t>
+  </si>
+  <si>
+    <t>有点意外</t>
+  </si>
+  <si>
+    <t>我在犯罪时肯定也难以承受沉重的罪恶感，所以我才选了坦白</t>
+  </si>
+  <si>
+    <t>犯过罪了吗</t>
+  </si>
+  <si>
+    <t>还没</t>
+  </si>
+  <si>
+    <t>还没？</t>
+  </si>
+  <si>
+    <t>人怎么会知道今后的事</t>
+  </si>
+  <si>
+    <t>要说的话倒是失忆的你更有可能犯罪吧</t>
+  </si>
+  <si>
+    <t>要这么说的话，我在失忆前干什么都有可能</t>
+  </si>
+  <si>
+    <t>不过关于坦白的事是一样的呢</t>
+  </si>
+  <si>
+    <t>另外，关于跟对方建立的信赖关系，你作何感想</t>
+  </si>
+  <si>
+    <t>也就是说，如果两人之间是关系亲近，互相信赖的好友，都保持沉默而获刑两年</t>
+  </si>
+  <si>
+    <t>或者背叛一方使自己获利</t>
+  </si>
+  <si>
+    <t>这些情况都没有想过吗</t>
+  </si>
+  <si>
+    <t>保持沉默真的很痛苦，，</t>
+  </si>
+  <si>
+    <t>确实，自从你醒来就一直在讲话</t>
+  </si>
+  <si>
+    <t>按这个势头，记忆逐渐就会恢复了</t>
+  </si>
+  <si>
+    <t>再说着这些的时候，有没有想起点什么</t>
+  </si>
+  <si>
+    <t>不用担心，可以直说</t>
+  </si>
+  <si>
+    <t>感觉什么罪都没有犯过，但是，，</t>
+  </si>
+  <si>
+    <t>不用强迫自己，对自己不利的事可以不用说</t>
+  </si>
+  <si>
+    <t>没事的</t>
+  </si>
+  <si>
+    <t>一下子说多了，对大脑的负担太重</t>
+  </si>
+  <si>
+    <t>今日的谈话就到此为止，是颇有意思的谈话</t>
+  </si>
+  <si>
+    <t>我该去看诊其他的患者了，如果没有疑问的话，我该走了</t>
+  </si>
+  <si>
+    <t>还有明天和后天的</t>
+  </si>
+  <si>
+    <t>明天，，必须得三天是吗</t>
+  </si>
+  <si>
+    <t>三天才能治好</t>
+  </si>
+  <si>
+    <t>三天治好？</t>
+  </si>
+  <si>
+    <t>向你保证</t>
+  </si>
+  <si>
+    <t>那么多人，有治好的吗</t>
+  </si>
+  <si>
+    <t>看诊过很多</t>
+  </si>
+  <si>
+    <t>全部都治好了？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全部都</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11.25"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>平安无事的回家了</t>
+    </r>
+  </si>
+  <si>
+    <t>都好好的治了？</t>
+  </si>
+  <si>
+    <t>是的</t>
+  </si>
+  <si>
+    <t>那么，第一天暂且相信你好了</t>
+  </si>
+  <si>
+    <t>谢谢，那么再见</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.25"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.25"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
-    <fill>
-      <patternFill/>
+  <fills count="34">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -473,157 +1011,163 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -678,74 +1222,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1478,789 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B94"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <cols>
+    <col min="2" max="2" width="79.2727272727273" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" spans="1:2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" ht="43.5" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="72.5" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="87" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="14.5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="29" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="72.5" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" ht="145" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="29" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="14.5" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" ht="87" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" ht="116" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="159.5" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="72.5" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" ht="29" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="87" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" ht="58" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" ht="72.5" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="87" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="116" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" ht="58" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" ht="58" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" ht="101.5" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" ht="72.5" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" ht="72.5" spans="1:2">
+      <c r="A28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" ht="58" spans="1:2">
+      <c r="A29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" ht="72.5" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" ht="72.5" spans="1:2">
+      <c r="A31" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" ht="43.5" spans="1:2">
+      <c r="A32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" ht="87" spans="1:2">
+      <c r="A33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" ht="72.5" spans="1:2">
+      <c r="A34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" ht="116" spans="1:2">
+      <c r="A35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" ht="58" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" ht="140.5" spans="1:2">
+      <c r="A37" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" ht="31.5" spans="1:2">
+      <c r="A38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" ht="130.5" spans="1:2">
+      <c r="A39" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" ht="14.5" spans="1:2">
+      <c r="A40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" ht="14.5" spans="1:2">
+      <c r="A41" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" ht="14.5" spans="1:2">
+      <c r="A42" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" ht="167" spans="1:2">
+      <c r="A43" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" ht="101.5" spans="1:2">
+      <c r="A44" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" ht="101.5" spans="1:2">
+      <c r="A45" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" ht="145" spans="1:2">
+      <c r="A46" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" ht="145" spans="1:2">
+      <c r="A47" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" ht="14.5" spans="1:2">
+      <c r="A48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" ht="14.5" spans="1:2">
+      <c r="A49" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" ht="72.5" spans="1:2">
+      <c r="A50" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" ht="43.5" spans="1:2">
+      <c r="A51" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" ht="116" spans="1:2">
+      <c r="A52" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" ht="87" spans="1:2">
+      <c r="A53" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" ht="87" spans="1:2">
+      <c r="A54" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" ht="29" spans="1:2">
+      <c r="A55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" ht="58" spans="1:2">
+      <c r="A56" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" ht="29" spans="1:2">
+      <c r="A57" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" ht="145" spans="1:2">
+      <c r="A58" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" ht="29" spans="1:2">
+      <c r="A59" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" ht="14.5" spans="1:2">
+      <c r="A60" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" ht="14.5" spans="1:2">
+      <c r="A61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" ht="58" spans="1:2">
+      <c r="A62" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" ht="87" spans="1:2">
+      <c r="A63" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" ht="101.5" spans="1:2">
+      <c r="A64" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" ht="72.5" spans="1:2">
+      <c r="A65" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" ht="116" spans="1:2">
+      <c r="A66" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" ht="174" spans="1:2">
+      <c r="A67" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" ht="58" spans="1:2">
+      <c r="A68" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" ht="58" spans="1:2">
+      <c r="A69" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" ht="58" spans="1:2">
+      <c r="A70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" ht="72.5" spans="1:2">
+      <c r="A71" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" ht="72.5" spans="1:2">
+      <c r="A72" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" ht="87" spans="1:2">
+      <c r="A73" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" ht="43.5" spans="1:2">
+      <c r="A74" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" ht="72.5" spans="1:2">
+      <c r="A75" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" ht="101.5" spans="1:2">
+      <c r="A76" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" ht="14.5" spans="1:2">
+      <c r="A77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" ht="87" spans="1:2">
+      <c r="A78" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" ht="101.5" spans="1:2">
+      <c r="A79" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" ht="130.5" spans="1:2">
+      <c r="A80" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" ht="14.5" spans="1:2">
+      <c r="A81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="82" ht="43.5" spans="1:2">
+      <c r="A82" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" ht="72.5" spans="1:2">
+      <c r="A83" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" ht="29" spans="1:2">
+      <c r="A84" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" ht="29" spans="1:2">
+      <c r="A85" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" ht="29" spans="1:2">
+      <c r="A86" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" ht="58" spans="1:2">
+      <c r="A87" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" ht="29" spans="1:2">
+      <c r="A88" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" ht="43.5" spans="1:2">
+      <c r="A89" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" ht="60.5" spans="1:2">
+      <c r="A90" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" ht="43.5" spans="1:2">
+      <c r="A91" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" ht="14.5" spans="1:2">
+      <c r="A92" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" ht="72.5" spans="1:2">
+      <c r="A93" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" ht="43.5" spans="1:2">
+      <c r="A94" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Resources/Story/1.xlsx
+++ b/Assets/Resources/Story/1.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="96">
   <si>
     <t>医生</t>
   </si>
@@ -266,6 +266,9 @@
     </r>
   </si>
   <si>
+    <t>ShowImageCG1</t>
+  </si>
+  <si>
     <t>这是为了让你记忆恢复的谈话，我跟你是一起犯罪的同伴</t>
   </si>
   <si>
@@ -359,6 +362,9 @@
     <t>一方缄默一方坦白时，缄默的刑期十年，而坦白的将会被释放</t>
   </si>
   <si>
+    <t>HideImageCG1</t>
+  </si>
+  <si>
     <t>在这样的情况下，你会选择缄默还是坦白，来跟我回答一下吧</t>
   </si>
   <si>
@@ -524,6 +530,9 @@
   </si>
   <si>
     <t>谢谢，那么再见</t>
+  </si>
+  <si>
+    <t>StartTL1</t>
   </si>
 </sst>
 </file>
@@ -1480,8 +1489,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:C94"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="79.2727272727273" customWidth="1"/>
   </cols>
@@ -1490,7 +1499,7 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" ht="43.5" spans="1:2">
+    <row r="2" ht="14.5" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1498,7 +1507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="72.5" spans="1:2">
+    <row r="3" ht="14.5" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1506,7 +1515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="87" spans="1:2">
+    <row r="4" ht="14.5" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="29" spans="1:2">
+    <row r="7" ht="14.5" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1546,7 +1555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="72.5" spans="1:2">
+    <row r="9" ht="14.5" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
@@ -1554,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" ht="145" spans="1:2">
+    <row r="10" ht="14.5" spans="1:2">
       <c r="A10" s="2" t="s">
         <v>0</v>
       </c>
@@ -1562,7 +1571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" ht="29" spans="1:2">
+    <row r="11" ht="14.5" spans="1:2">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -1586,7 +1595,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" ht="87" spans="1:2">
+    <row r="14" ht="14.5" spans="1:2">
       <c r="A14" s="2" t="s">
         <v>0</v>
       </c>
@@ -1594,7 +1603,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" ht="116" spans="1:2">
+    <row r="15" ht="14.5" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>2</v>
       </c>
@@ -1602,7 +1611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" ht="159.5" spans="1:2">
+    <row r="16" ht="14.5" spans="1:2">
       <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
@@ -1610,7 +1619,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" ht="72.5" spans="1:2">
+    <row r="17" ht="14.5" spans="1:2">
       <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
@@ -1618,7 +1627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" ht="29" spans="1:2">
+    <row r="18" ht="14.5" spans="1:2">
       <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
@@ -1626,7 +1635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" ht="87" spans="1:2">
+    <row r="19" ht="14.5" spans="1:2">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -1634,7 +1643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" ht="58" spans="1:2">
+    <row r="20" ht="14.5" spans="1:2">
       <c r="A20" s="2" t="s">
         <v>2</v>
       </c>
@@ -1642,7 +1651,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" ht="72.5" spans="1:2">
+    <row r="21" ht="14.5" spans="1:2">
       <c r="A21" s="2" t="s">
         <v>0</v>
       </c>
@@ -1650,7 +1659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" ht="87" spans="1:2">
+    <row r="22" ht="14.5" spans="1:2">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -1658,7 +1667,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" ht="116" spans="1:2">
+    <row r="23" ht="14.5" spans="1:2">
       <c r="A23" s="2" t="s">
         <v>0</v>
       </c>
@@ -1666,7 +1675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="58" spans="1:2">
+    <row r="24" ht="14.5" spans="1:2">
       <c r="A24" s="2" t="s">
         <v>0</v>
       </c>
@@ -1674,7 +1683,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="58" spans="1:2">
+    <row r="25" ht="14.5" spans="1:2">
       <c r="A25" s="2" t="s">
         <v>2</v>
       </c>
@@ -1682,7 +1691,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" ht="101.5" spans="1:2">
+    <row r="26" ht="14.5" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>0</v>
       </c>
@@ -1690,7 +1699,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" ht="72.5" spans="1:2">
+    <row r="27" ht="14.5" spans="1:2">
       <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
@@ -1698,7 +1707,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" ht="72.5" spans="1:2">
+    <row r="28" ht="14.5" spans="1:2">
       <c r="A28" s="2" t="s">
         <v>0</v>
       </c>
@@ -1706,7 +1715,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" ht="58" spans="1:2">
+    <row r="29" ht="14.5" spans="1:2">
       <c r="A29" s="2" t="s">
         <v>2</v>
       </c>
@@ -1714,7 +1723,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" ht="72.5" spans="1:2">
+    <row r="30" ht="14.5" spans="1:2">
       <c r="A30" s="2" t="s">
         <v>0</v>
       </c>
@@ -1722,7 +1731,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" ht="72.5" spans="1:2">
+    <row r="31" ht="14.5" spans="1:2">
       <c r="A31" s="2" t="s">
         <v>0</v>
       </c>
@@ -1730,7 +1739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" ht="43.5" spans="1:2">
+    <row r="32" ht="14.5" spans="1:2">
       <c r="A32" s="2" t="s">
         <v>2</v>
       </c>
@@ -1738,7 +1747,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" ht="87" spans="1:2">
+    <row r="33" ht="14.5" spans="1:3">
       <c r="A33" s="2" t="s">
         <v>0</v>
       </c>
@@ -1746,7 +1755,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" ht="72.5" spans="1:2">
+    <row r="34" ht="14.5" spans="1:3">
       <c r="A34" s="2" t="s">
         <v>2</v>
       </c>
@@ -1754,7 +1763,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" ht="116" spans="1:2">
+    <row r="35" ht="14.5" spans="1:3">
       <c r="A35" s="2" t="s">
         <v>0</v>
       </c>
@@ -1762,7 +1771,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" ht="58" spans="1:2">
+    <row r="36" ht="14.5" spans="1:3">
       <c r="A36" s="2" t="s">
         <v>2</v>
       </c>
@@ -1770,7 +1779,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" ht="140.5" spans="1:2">
+    <row r="37" ht="17" spans="1:3">
       <c r="A37" s="2" t="s">
         <v>0</v>
       </c>
@@ -1778,92 +1787,98 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="31.5" spans="1:2">
+    <row r="38" ht="17" spans="1:3">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" ht="130.5" spans="1:2">
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" ht="14.5" spans="1:3">
       <c r="A39" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" ht="14.5" spans="1:2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" ht="14.5" spans="1:3">
       <c r="A40" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" ht="14.5" spans="1:2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" ht="14.5" spans="1:3">
       <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" ht="14.5" spans="1:2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" ht="14.5" spans="1:3">
       <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" ht="167" spans="1:2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" ht="17" spans="1:3">
       <c r="A43" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" ht="101.5" spans="1:2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" ht="14.5" spans="1:3">
       <c r="A44" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" ht="101.5" spans="1:2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" ht="14.5" spans="1:3">
       <c r="A45" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" ht="145" spans="1:2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" ht="14.5" spans="1:3">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" ht="145" spans="1:2">
+        <v>47</v>
+      </c>
+      <c r="C46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" ht="14.5" spans="1:3">
       <c r="A47" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" ht="14.5" spans="1:2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" ht="14.5" spans="1:3">
       <c r="A48" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" ht="14.5" spans="1:2">
@@ -1871,87 +1886,87 @@
         <v>0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" ht="72.5" spans="1:2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" ht="14.5" spans="1:2">
       <c r="A50" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" ht="43.5" spans="1:2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" ht="14.5" spans="1:2">
       <c r="A51" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" ht="116" spans="1:2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" ht="14.5" spans="1:2">
       <c r="A52" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" ht="87" spans="1:2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" ht="14.5" spans="1:2">
       <c r="A53" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" ht="87" spans="1:2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" ht="14.5" spans="1:2">
       <c r="A54" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" ht="29" spans="1:2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" ht="14.5" spans="1:2">
       <c r="A55" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" ht="58" spans="1:2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" ht="14.5" spans="1:2">
       <c r="A56" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" ht="29" spans="1:2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" ht="14.5" spans="1:2">
       <c r="A57" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" ht="145" spans="1:2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" ht="14.5" spans="1:2">
       <c r="A58" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" ht="29" spans="1:2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" ht="14.5" spans="1:2">
       <c r="A59" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" ht="14.5" spans="1:2">
@@ -1959,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" ht="14.5" spans="1:2">
@@ -1967,127 +1982,127 @@
         <v>2</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" ht="58" spans="1:2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" ht="14.5" spans="1:2">
       <c r="A62" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" ht="87" spans="1:2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" ht="14.5" spans="1:2">
       <c r="A63" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" ht="101.5" spans="1:2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" ht="14.5" spans="1:2">
       <c r="A64" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" ht="72.5" spans="1:2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" ht="14.5" spans="1:2">
       <c r="A65" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" ht="116" spans="1:2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" ht="14.5" spans="1:2">
       <c r="A66" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" ht="174" spans="1:2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" ht="14.5" spans="1:2">
       <c r="A67" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" ht="58" spans="1:2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" ht="14.5" spans="1:2">
       <c r="A68" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" ht="58" spans="1:2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69" ht="14.5" spans="1:2">
       <c r="A69" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" ht="58" spans="1:2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="70" ht="14.5" spans="1:2">
       <c r="A70" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" ht="72.5" spans="1:2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" ht="14.5" spans="1:2">
       <c r="A71" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" ht="72.5" spans="1:2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" ht="14.5" spans="1:2">
       <c r="A72" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" ht="87" spans="1:2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" ht="14.5" spans="1:2">
       <c r="A73" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" ht="43.5" spans="1:2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" ht="14.5" spans="1:2">
       <c r="A74" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" ht="72.5" spans="1:2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" ht="14.5" spans="1:2">
       <c r="A75" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" ht="101.5" spans="1:2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" ht="14.5" spans="1:2">
       <c r="A76" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" ht="14.5" spans="1:2">
@@ -2095,143 +2110,146 @@
         <v>2</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" ht="87" spans="1:2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" ht="14.5" spans="1:2">
       <c r="A78" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" ht="101.5" spans="1:2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" ht="14.5" spans="1:2">
       <c r="A79" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" ht="130.5" spans="1:2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" ht="14.5" spans="1:2">
       <c r="A80" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" ht="14.5" spans="1:2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" ht="14.5" spans="1:3">
       <c r="A81" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="82" ht="43.5" spans="1:2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82" ht="14.5" spans="1:3">
       <c r="A82" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" ht="72.5" spans="1:2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" ht="14.5" spans="1:3">
       <c r="A83" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" ht="29" spans="1:2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" ht="14.5" spans="1:3">
       <c r="A84" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" ht="29" spans="1:2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" ht="14.5" spans="1:3">
       <c r="A85" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" ht="29" spans="1:2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" ht="14.5" spans="1:3">
       <c r="A86" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="87" ht="58" spans="1:2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" ht="14.5" spans="1:3">
       <c r="A87" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" ht="29" spans="1:2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" ht="14.5" spans="1:3">
       <c r="A88" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" ht="43.5" spans="1:2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" ht="14.5" spans="1:3">
       <c r="A89" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" ht="60.5" spans="1:2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" ht="17" spans="1:3">
       <c r="A90" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" ht="43.5" spans="1:2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" ht="14.5" spans="1:3">
       <c r="A91" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" ht="14.5" spans="1:2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" ht="14.5" spans="1:3">
       <c r="A92" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" ht="72.5" spans="1:2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" ht="14.5" spans="1:3">
       <c r="A93" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" ht="43.5" spans="1:2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" ht="14.5" spans="1:3">
       <c r="A94" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="C94" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
